--- a/attendance.xlsx
+++ b/attendance.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="114">
   <si>
     <t>ID</t>
   </si>
@@ -140,6 +140,222 @@
   </si>
   <si>
     <t>21:43:27</t>
+  </si>
+  <si>
+    <t>2026-03-08</t>
+  </si>
+  <si>
+    <t>12:52:47</t>
+  </si>
+  <si>
+    <t>13:27:39</t>
+  </si>
+  <si>
+    <t>S001</t>
+  </si>
+  <si>
+    <t>Test Student</t>
+  </si>
+  <si>
+    <t>13:37:11</t>
+  </si>
+  <si>
+    <t>device-test-001</t>
+  </si>
+  <si>
+    <t>uploads/selfies/S001_1772957231289.jpg</t>
+  </si>
+  <si>
+    <t>S002</t>
+  </si>
+  <si>
+    <t>Student 2</t>
+  </si>
+  <si>
+    <t>13:38:31</t>
+  </si>
+  <si>
+    <t>device-test-002</t>
+  </si>
+  <si>
+    <t>uploads/selfies/S002_1772957311170.jpg</t>
+  </si>
+  <si>
+    <t>S003</t>
+  </si>
+  <si>
+    <t>Student 3</t>
+  </si>
+  <si>
+    <t>device-test-003</t>
+  </si>
+  <si>
+    <t>uploads/selfies/S003_1772957311244.jpg</t>
+  </si>
+  <si>
+    <t>123</t>
+  </si>
+  <si>
+    <t>13:44:27</t>
+  </si>
+  <si>
+    <t>dfbf771e-c1b1-415d-87ac-962b632d3c00</t>
+  </si>
+  <si>
+    <t>uploads/selfies/123_1772957667343.jpg</t>
+  </si>
+  <si>
+    <t>01</t>
+  </si>
+  <si>
+    <t>Ronak1</t>
+  </si>
+  <si>
+    <t>13:52:03</t>
+  </si>
+  <si>
+    <t>uploads/selfies/01_1772958123696.jpg</t>
+  </si>
+  <si>
+    <t>14:02:53</t>
+  </si>
+  <si>
+    <t>uploads/selfies/01_1772958773001.jpg</t>
+  </si>
+  <si>
+    <t>02</t>
+  </si>
+  <si>
+    <t>Ronak2</t>
+  </si>
+  <si>
+    <t>14:03:16</t>
+  </si>
+  <si>
+    <t>uploads/selfies/02_1772958796862.jpg</t>
+  </si>
+  <si>
+    <t>03</t>
+  </si>
+  <si>
+    <t>Ronak3</t>
+  </si>
+  <si>
+    <t>14:03:56</t>
+  </si>
+  <si>
+    <t>uploads/selfies/03_1772958836699.jpg</t>
+  </si>
+  <si>
+    <t>DKMD</t>
+  </si>
+  <si>
+    <t>DCK</t>
+  </si>
+  <si>
+    <t>14:04:10</t>
+  </si>
+  <si>
+    <t>uploads/selfies/DKMD_1772958850176.jpg</t>
+  </si>
+  <si>
+    <t>DKMDQQ</t>
+  </si>
+  <si>
+    <t>DCKW</t>
+  </si>
+  <si>
+    <t>14:05:06</t>
+  </si>
+  <si>
+    <t>uploads/selfies/DKMDQQ_1772958906249.jpg</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>14:06:44</t>
+  </si>
+  <si>
+    <t>uploads/selfies/11_1772959004510.jpg</t>
+  </si>
+  <si>
+    <t>14:07:09</t>
+  </si>
+  <si>
+    <t>uploads/selfies/11_1772959029826.jpg</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>Ronak111</t>
+  </si>
+  <si>
+    <t>14:07:41</t>
+  </si>
+  <si>
+    <t>uploads/selfies/32_1772959061359.jpg</t>
+  </si>
+  <si>
+    <t>32S</t>
+  </si>
+  <si>
+    <t>14:07:50</t>
+  </si>
+  <si>
+    <t>uploads/selfies/32S_1772959070916.jpg</t>
+  </si>
+  <si>
+    <t>23112025H</t>
+  </si>
+  <si>
+    <t>14:08:40</t>
+  </si>
+  <si>
+    <t>uploads/selfies/23112025H_1772959120773.jpg</t>
+  </si>
+  <si>
+    <t>23112020</t>
+  </si>
+  <si>
+    <t>ALSOH</t>
+  </si>
+  <si>
+    <t>14:09:17</t>
+  </si>
+  <si>
+    <t>uploads/selfies/23112020_1772959157132.jpg</t>
+  </si>
+  <si>
+    <t>14:09:24</t>
+  </si>
+  <si>
+    <t>uploads/selfies/23112020_1772959164820.jpg</t>
+  </si>
+  <si>
+    <t>23112020Q</t>
+  </si>
+  <si>
+    <t>14:09:45</t>
+  </si>
+  <si>
+    <t>uploads/selfies/23112020Q_1772959185511.jpg</t>
+  </si>
+  <si>
+    <t>14:09:53</t>
+  </si>
+  <si>
+    <t>uploads/selfies/23112020Q_1772959193719.jpg</t>
+  </si>
+  <si>
+    <t>23112020QQ</t>
+  </si>
+  <si>
+    <t>14:10:23</t>
+  </si>
+  <si>
+    <t>uploads/selfies/23112020QQ_1772959223037.jpg</t>
   </si>
 </sst>
 </file>
@@ -570,7 +786,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:H44"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -943,6 +1159,586 @@
         <v>10</v>
       </c>
     </row>
+    <row r="22" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F22" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F23" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F24" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F25" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F26" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F27" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F28" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F29" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F30" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F31" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F32" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F33" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F34" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F35" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F36" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F37" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G37" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F38" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F39" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G39" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F40" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F41" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G41" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F42" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F43" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G43" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F44" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G44" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>113</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>

--- a/attendance.xlsx
+++ b/attendance.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="122">
   <si>
     <t>ID</t>
   </si>
@@ -356,6 +356,30 @@
   </si>
   <si>
     <t>uploads/selfies/23112020QQ_1772959223037.jpg</t>
+  </si>
+  <si>
+    <t>110326h</t>
+  </si>
+  <si>
+    <t>2026-03-11</t>
+  </si>
+  <si>
+    <t>09:52:28</t>
+  </si>
+  <si>
+    <t>uploads/selfies/110326h_1773202948389.jpg</t>
+  </si>
+  <si>
+    <t>110326</t>
+  </si>
+  <si>
+    <t>RonakN</t>
+  </si>
+  <si>
+    <t>09:53:16</t>
+  </si>
+  <si>
+    <t>uploads/selfies/110326_1773202996230.jpg</t>
   </si>
 </sst>
 </file>
@@ -786,7 +810,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H44"/>
+  <dimension ref="A1:H46"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -1739,6 +1763,58 @@
         <v>113</v>
       </c>
     </row>
+    <row r="45" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F45" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G45" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F46" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G46" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
